--- a/utils/data-room-simulator/output/nwc_schedule.xlsx
+++ b/utils/data-room-simulator/output/nwc_schedule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWC Schedule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NWC Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,71 +413,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>accounts_receivable</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>inventory</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prepaid_expenses</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_current_assets</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accounts_payable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>accrued_expenses</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>deferred_revenue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>total_current_liabilities</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>net_working_capital</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>operating_nwc</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>nwc_as_pct_revenue</t>
         </is>
@@ -502,40 +490,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57203.96</v>
+        <v>32487.68</v>
       </c>
       <c r="C2" t="n">
-        <v>4179999.49</v>
+        <v>2563729.71</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>57203.96</v>
+        <v>32487.68</v>
       </c>
       <c r="F2" t="n">
-        <v>4294407.41</v>
+        <v>2628705.07</v>
       </c>
       <c r="G2" t="n">
-        <v>967799.36</v>
+        <v>744547.1800000001</v>
       </c>
       <c r="H2" t="n">
-        <v>85805.95</v>
+        <v>48731.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2412902.93</v>
+        <v>2234626.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3466508.24</v>
+        <v>3027904.85</v>
       </c>
       <c r="K2" t="n">
-        <v>827899.17</v>
+        <v>-399199.78</v>
       </c>
       <c r="L2" t="n">
-        <v>770695.21</v>
+        <v>-431687.46</v>
       </c>
       <c r="M2" t="n">
-        <v>26.9</v>
+        <v>-26.6</v>
       </c>
     </row>
     <row r="3">
@@ -545,40 +533,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61686.96</v>
+        <v>32388.74</v>
       </c>
       <c r="C3" t="n">
-        <v>4911728.21</v>
+        <v>2282617.17</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>61686.96</v>
+        <v>32388.74</v>
       </c>
       <c r="F3" t="n">
-        <v>5035102.13</v>
+        <v>2347394.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1327300.07</v>
+        <v>799618.03</v>
       </c>
       <c r="H3" t="n">
-        <v>92530.42999999999</v>
+        <v>48583.11</v>
       </c>
       <c r="I3" t="n">
-        <v>3162311.15</v>
+        <v>2167428.67</v>
       </c>
       <c r="J3" t="n">
-        <v>4582141.65</v>
+        <v>3015629.81</v>
       </c>
       <c r="K3" t="n">
-        <v>452960.48</v>
+        <v>-668235.16</v>
       </c>
       <c r="L3" t="n">
-        <v>391273.52</v>
+        <v>-700623.9</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7</v>
+        <v>-43.3</v>
       </c>
     </row>
     <row r="4">
@@ -588,40 +576,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58008.96</v>
+        <v>35357.45</v>
       </c>
       <c r="C4" t="n">
-        <v>4755305.71</v>
+        <v>2764544.78</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>58008.96</v>
+        <v>35357.45</v>
       </c>
       <c r="F4" t="n">
-        <v>4871323.63</v>
+        <v>2835259.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1115030.94</v>
+        <v>883406.33</v>
       </c>
       <c r="H4" t="n">
-        <v>87013.45</v>
+        <v>53036.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2583851.5</v>
+        <v>1500221.02</v>
       </c>
       <c r="J4" t="n">
-        <v>3785895.89</v>
+        <v>2436663.53</v>
       </c>
       <c r="K4" t="n">
-        <v>1085427.74</v>
+        <v>398596.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1027418.78</v>
+        <v>363238.7</v>
       </c>
       <c r="M4" t="n">
-        <v>35.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
@@ -631,40 +619,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65733.63</v>
+        <v>38349.37</v>
       </c>
       <c r="C5" t="n">
-        <v>4400624.66</v>
+        <v>3161109.21</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>65733.63</v>
+        <v>38349.37</v>
       </c>
       <c r="F5" t="n">
-        <v>4532091.92</v>
+        <v>3237807.95</v>
       </c>
       <c r="G5" t="n">
-        <v>1200771.37</v>
+        <v>750410.97</v>
       </c>
       <c r="H5" t="n">
-        <v>98600.45</v>
+        <v>57524.06</v>
       </c>
       <c r="I5" t="n">
-        <v>3470317.06</v>
+        <v>1816707.85</v>
       </c>
       <c r="J5" t="n">
-        <v>4769688.88</v>
+        <v>2624642.88</v>
       </c>
       <c r="K5" t="n">
-        <v>-237596.96</v>
+        <v>613165.0699999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-303330.59</v>
+        <v>574815.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.199999999999999</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -674,40 +662,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66980.49000000001</v>
+        <v>38435.07</v>
       </c>
       <c r="C6" t="n">
-        <v>5509573.25</v>
+        <v>3025339.06</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>66980.49000000001</v>
+        <v>38435.07</v>
       </c>
       <c r="F6" t="n">
-        <v>5643534.23</v>
+        <v>3102209.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1088543.67</v>
+        <v>815320.5600000001</v>
       </c>
       <c r="H6" t="n">
-        <v>100470.73</v>
+        <v>57652.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2779063.49</v>
+        <v>1933296.81</v>
       </c>
       <c r="J6" t="n">
-        <v>3968077.89</v>
+        <v>2806269.97</v>
       </c>
       <c r="K6" t="n">
-        <v>1675456.34</v>
+        <v>295939.23</v>
       </c>
       <c r="L6" t="n">
-        <v>1608475.85</v>
+        <v>257504.16</v>
       </c>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -717,40 +705,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>480389.62</v>
+        <v>38822.95</v>
       </c>
       <c r="C7" t="n">
-        <v>5150250.43</v>
+        <v>3224199.57</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>70576.5</v>
+        <v>38822.95</v>
       </c>
       <c r="F7" t="n">
-        <v>5701216.55</v>
+        <v>3301845.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1438804.62</v>
+        <v>947195.67</v>
       </c>
       <c r="H7" t="n">
-        <v>105864.75</v>
+        <v>58234.42</v>
       </c>
       <c r="I7" t="n">
-        <v>4496557</v>
+        <v>2196243.13</v>
       </c>
       <c r="J7" t="n">
-        <v>6041226.37</v>
+        <v>3201673.22</v>
       </c>
       <c r="K7" t="n">
-        <v>-340009.82</v>
+        <v>100172.25</v>
       </c>
       <c r="L7" t="n">
-        <v>-820399.4399999999</v>
+        <v>61349.3</v>
       </c>
       <c r="M7" t="n">
-        <v>-23.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -760,40 +748,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1444116.49</v>
+        <v>271205.16</v>
       </c>
       <c r="C8" t="n">
-        <v>5085938.77</v>
+        <v>2923729.98</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75738.02</v>
+        <v>43327.19</v>
       </c>
       <c r="F8" t="n">
-        <v>6605793.28</v>
+        <v>3238262.33</v>
       </c>
       <c r="G8" t="n">
-        <v>1633371.99</v>
+        <v>925724.33</v>
       </c>
       <c r="H8" t="n">
-        <v>113607.04</v>
+        <v>64990.79</v>
       </c>
       <c r="I8" t="n">
-        <v>4453012.67</v>
+        <v>2645653.64</v>
       </c>
       <c r="J8" t="n">
-        <v>6199991.7</v>
+        <v>3636368.76</v>
       </c>
       <c r="K8" t="n">
-        <v>405801.58</v>
+        <v>-398106.43</v>
       </c>
       <c r="L8" t="n">
-        <v>-1038314.91</v>
+        <v>-669311.59</v>
       </c>
       <c r="M8" t="n">
-        <v>-27.4</v>
+        <v>-30.9</v>
       </c>
     </row>
     <row r="9">
@@ -803,40 +791,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>289775.31</v>
+        <v>1010952.54</v>
       </c>
       <c r="C9" t="n">
-        <v>5717669.78</v>
+        <v>2774784.58</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>74360.42999999999</v>
+        <v>41163.09</v>
       </c>
       <c r="F9" t="n">
-        <v>6081805.52</v>
+        <v>3826900.21</v>
       </c>
       <c r="G9" t="n">
-        <v>1237469.87</v>
+        <v>847372.13</v>
       </c>
       <c r="H9" t="n">
-        <v>111540.64</v>
+        <v>61744.64</v>
       </c>
       <c r="I9" t="n">
-        <v>3594285.6</v>
+        <v>3021773.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4943296.11</v>
+        <v>3930890.07</v>
       </c>
       <c r="K9" t="n">
-        <v>1138509.41</v>
+        <v>-103989.86</v>
       </c>
       <c r="L9" t="n">
-        <v>848734.1</v>
+        <v>-1114942.4</v>
       </c>
       <c r="M9" t="n">
-        <v>22.8</v>
+        <v>-54.2</v>
       </c>
     </row>
     <row r="10">
@@ -846,40 +834,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3604446.53</v>
+        <v>1117449.2</v>
       </c>
       <c r="C10" t="n">
-        <v>5533368.47</v>
+        <v>3217152.87</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>79235.85000000001</v>
+        <v>44753.5</v>
       </c>
       <c r="F10" t="n">
-        <v>9217050.85</v>
+        <v>4379355.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1399394.83</v>
+        <v>1051327</v>
       </c>
       <c r="H10" t="n">
-        <v>118853.78</v>
+        <v>67130.25</v>
       </c>
       <c r="I10" t="n">
-        <v>5780659.62</v>
+        <v>3045932.11</v>
       </c>
       <c r="J10" t="n">
-        <v>7298908.23</v>
+        <v>4164389.36</v>
       </c>
       <c r="K10" t="n">
-        <v>1918142.62</v>
+        <v>214966.21</v>
       </c>
       <c r="L10" t="n">
-        <v>-1686303.91</v>
+        <v>-902482.99</v>
       </c>
       <c r="M10" t="n">
-        <v>-42.6</v>
+        <v>-40.3</v>
       </c>
     </row>
     <row r="11">
@@ -889,40 +877,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2594536.58</v>
+        <v>579582.22</v>
       </c>
       <c r="C11" t="n">
-        <v>6963719.49</v>
+        <v>4013111.94</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>92228.72</v>
+        <v>49214.65</v>
       </c>
       <c r="F11" t="n">
-        <v>9650484.789999999</v>
+        <v>4641908.81</v>
       </c>
       <c r="G11" t="n">
-        <v>1733033.63</v>
+        <v>1022957.59</v>
       </c>
       <c r="H11" t="n">
-        <v>138343.09</v>
+        <v>73821.97</v>
       </c>
       <c r="I11" t="n">
-        <v>4956479.31</v>
+        <v>2980359.38</v>
       </c>
       <c r="J11" t="n">
-        <v>6827856.03</v>
+        <v>4077138.94</v>
       </c>
       <c r="K11" t="n">
-        <v>2822628.76</v>
+        <v>564769.87</v>
       </c>
       <c r="L11" t="n">
-        <v>228092.18</v>
+        <v>-14812.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="12">
@@ -932,40 +920,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3969855.89</v>
+        <v>1275447.67</v>
       </c>
       <c r="C12" t="n">
-        <v>7177547.28</v>
+        <v>3865678.06</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>87255.06</v>
+        <v>51944.7</v>
       </c>
       <c r="F12" t="n">
-        <v>11234658.23</v>
+        <v>5193070.43</v>
       </c>
       <c r="G12" t="n">
-        <v>1614701.81</v>
+        <v>987434.45</v>
       </c>
       <c r="H12" t="n">
-        <v>130882.6</v>
+        <v>77917.03999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>5809584.73</v>
+        <v>3194242.41</v>
       </c>
       <c r="J12" t="n">
-        <v>7555169.14</v>
+        <v>4259593.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3679489.09</v>
+        <v>933476.53</v>
       </c>
       <c r="L12" t="n">
-        <v>-290366.8</v>
+        <v>-341971.14</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.7</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="13">
@@ -975,40 +963,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6036389.43</v>
+        <v>2278794.93</v>
       </c>
       <c r="C13" t="n">
-        <v>6102853.62</v>
+        <v>3944970.63</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>83915.96000000001</v>
+        <v>53447.76</v>
       </c>
       <c r="F13" t="n">
-        <v>12223159.01</v>
+        <v>6277213.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1760429.06</v>
+        <v>991313.83</v>
       </c>
       <c r="H13" t="n">
-        <v>125873.95</v>
+        <v>80171.64</v>
       </c>
       <c r="I13" t="n">
-        <v>5832440.58</v>
+        <v>3893107.89</v>
       </c>
       <c r="J13" t="n">
-        <v>7718743.59</v>
+        <v>4964593.36</v>
       </c>
       <c r="K13" t="n">
-        <v>4504415.42</v>
+        <v>1312619.96</v>
       </c>
       <c r="L13" t="n">
-        <v>-1531974.01</v>
+        <v>-966174.97</v>
       </c>
       <c r="M13" t="n">
-        <v>-36.5</v>
+        <v>-36.2</v>
       </c>
     </row>
     <row r="14">
@@ -1018,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4720698.5</v>
+        <v>1925490.65</v>
       </c>
       <c r="C14" t="n">
-        <v>5009495.16</v>
+        <v>2880680.33</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>67018.62</v>
+        <v>41084.27</v>
       </c>
       <c r="F14" t="n">
-        <v>9797212.279999999</v>
+        <v>4847255.25</v>
       </c>
       <c r="G14" t="n">
-        <v>1178416.03</v>
+        <v>1043607.05</v>
       </c>
       <c r="H14" t="n">
-        <v>100527.92</v>
+        <v>61626.41</v>
       </c>
       <c r="I14" t="n">
-        <v>3351019.76</v>
+        <v>2135500.75</v>
       </c>
       <c r="J14" t="n">
-        <v>4629963.71</v>
+        <v>3240734.21</v>
       </c>
       <c r="K14" t="n">
-        <v>5167248.57</v>
+        <v>1606521.04</v>
       </c>
       <c r="L14" t="n">
-        <v>446550.07</v>
+        <v>-318969.61</v>
       </c>
       <c r="M14" t="n">
-        <v>13.3</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="15">
@@ -1061,40 +1049,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5069961.03</v>
+        <v>1647168.75</v>
       </c>
       <c r="C15" t="n">
-        <v>5564610.19</v>
+        <v>3385107.23</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>69219.84</v>
+        <v>44068.13</v>
       </c>
       <c r="F15" t="n">
-        <v>10703791.06</v>
+        <v>5076344.11</v>
       </c>
       <c r="G15" t="n">
-        <v>1487383.79</v>
+        <v>1006619.88</v>
       </c>
       <c r="H15" t="n">
-        <v>103829.76</v>
+        <v>66102.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3261242.78</v>
+        <v>2082545.62</v>
       </c>
       <c r="J15" t="n">
-        <v>4852456.33</v>
+        <v>3155267.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5851334.73</v>
+        <v>1921076.41</v>
       </c>
       <c r="L15" t="n">
-        <v>781373.7</v>
+        <v>273907.66</v>
       </c>
       <c r="M15" t="n">
-        <v>22.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="16">
@@ -1104,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6463214.06</v>
+        <v>1671217.01</v>
       </c>
       <c r="C16" t="n">
-        <v>4977042.64</v>
+        <v>3621561.97</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>66600.24000000001</v>
+        <v>45130.79</v>
       </c>
       <c r="F16" t="n">
-        <v>11506856.94</v>
+        <v>5337909.77</v>
       </c>
       <c r="G16" t="n">
-        <v>1097304.31</v>
+        <v>890970.6800000001</v>
       </c>
       <c r="H16" t="n">
-        <v>99900.36</v>
+        <v>67696.19</v>
       </c>
       <c r="I16" t="n">
-        <v>3799258.15</v>
+        <v>2136213.12</v>
       </c>
       <c r="J16" t="n">
-        <v>4996462.82</v>
+        <v>3094879.99</v>
       </c>
       <c r="K16" t="n">
-        <v>6510394.12</v>
+        <v>2243029.78</v>
       </c>
       <c r="L16" t="n">
-        <v>47180.06</v>
+        <v>571812.77</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="17">
@@ -1147,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8207403.57</v>
+        <v>2325553.9</v>
       </c>
       <c r="C17" t="n">
-        <v>5209509.73</v>
+        <v>3995253.12</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>71256.62</v>
+        <v>50243.67</v>
       </c>
       <c r="F17" t="n">
-        <v>13488169.92</v>
+        <v>6371050.69</v>
       </c>
       <c r="G17" t="n">
-        <v>1519827.79</v>
+        <v>1227807.5</v>
       </c>
       <c r="H17" t="n">
-        <v>106884.92</v>
+        <v>75365.5</v>
       </c>
       <c r="I17" t="n">
-        <v>4647181.14</v>
+        <v>2467550.02</v>
       </c>
       <c r="J17" t="n">
-        <v>6273893.85</v>
+        <v>3770723.02</v>
       </c>
       <c r="K17" t="n">
-        <v>7214276.07</v>
+        <v>2600327.67</v>
       </c>
       <c r="L17" t="n">
-        <v>-993127.5</v>
+        <v>274773.77</v>
       </c>
       <c r="M17" t="n">
-        <v>-27.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="18">
@@ -1190,40 +1178,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7490158.07</v>
+        <v>3055991.14</v>
       </c>
       <c r="C18" t="n">
-        <v>5117743.84</v>
+        <v>3749456.33</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>75102.52</v>
+        <v>49977.52</v>
       </c>
       <c r="F18" t="n">
-        <v>12683004.43</v>
+        <v>6855424.99</v>
       </c>
       <c r="G18" t="n">
-        <v>1603574.28</v>
+        <v>1260849.76</v>
       </c>
       <c r="H18" t="n">
-        <v>112653.78</v>
+        <v>74966.28</v>
       </c>
       <c r="I18" t="n">
-        <v>3011576.38</v>
+        <v>2563754.16</v>
       </c>
       <c r="J18" t="n">
-        <v>4727804.44</v>
+        <v>3899570.2</v>
       </c>
       <c r="K18" t="n">
-        <v>7955199.99</v>
+        <v>2955854.79</v>
       </c>
       <c r="L18" t="n">
-        <v>465041.92</v>
+        <v>-100136.35</v>
       </c>
       <c r="M18" t="n">
-        <v>12.4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="19">
@@ -1233,40 +1221,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7809696.26</v>
+        <v>3681670.11</v>
       </c>
       <c r="C19" t="n">
-        <v>5559515.74</v>
+        <v>3979795.5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>70224.48</v>
+        <v>50637.76</v>
       </c>
       <c r="F19" t="n">
-        <v>13439436.48</v>
+        <v>7712103.37</v>
       </c>
       <c r="G19" t="n">
-        <v>1532864.99</v>
+        <v>1256445.81</v>
       </c>
       <c r="H19" t="n">
-        <v>105336.72</v>
+        <v>75956.64</v>
       </c>
       <c r="I19" t="n">
-        <v>3151818.71</v>
+        <v>3063697.67</v>
       </c>
       <c r="J19" t="n">
-        <v>4790020.42</v>
+        <v>4396100.12</v>
       </c>
       <c r="K19" t="n">
-        <v>8649416.060000001</v>
+        <v>3316003.25</v>
       </c>
       <c r="L19" t="n">
-        <v>839719.8</v>
+        <v>-365666.86</v>
       </c>
       <c r="M19" t="n">
-        <v>23.9</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="20">
@@ -1276,40 +1264,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9159523.880000001</v>
+        <v>2935629.12</v>
       </c>
       <c r="C20" t="n">
-        <v>5526185.75</v>
+        <v>4475964.28</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>73385.62</v>
+        <v>53753.61</v>
       </c>
       <c r="F20" t="n">
-        <v>14759095.25</v>
+        <v>7465347.01</v>
       </c>
       <c r="G20" t="n">
-        <v>1286394.64</v>
+        <v>1057444.79</v>
       </c>
       <c r="H20" t="n">
-        <v>110078.43</v>
+        <v>80630.42</v>
       </c>
       <c r="I20" t="n">
-        <v>3988521.69</v>
+        <v>2629555.04</v>
       </c>
       <c r="J20" t="n">
-        <v>5384994.76</v>
+        <v>3767630.25</v>
       </c>
       <c r="K20" t="n">
-        <v>9374100.49</v>
+        <v>3697716.76</v>
       </c>
       <c r="L20" t="n">
-        <v>214576.61</v>
+        <v>762087.64</v>
       </c>
       <c r="M20" t="n">
-        <v>5.8</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="21">
@@ -1319,40 +1307,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8426825.800000001</v>
+        <v>3116414.21</v>
       </c>
       <c r="C21" t="n">
-        <v>6220206.92</v>
+        <v>4199950.05</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>76435.52</v>
+        <v>51489.71</v>
       </c>
       <c r="F21" t="n">
-        <v>14723468.24</v>
+        <v>7367853.97</v>
       </c>
       <c r="G21" t="n">
-        <v>1302060.48</v>
+        <v>1040533.72</v>
       </c>
       <c r="H21" t="n">
-        <v>114653.28</v>
+        <v>77234.57000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>3178569.22</v>
+        <v>2186210.62</v>
       </c>
       <c r="J21" t="n">
-        <v>4595282.98</v>
+        <v>3303978.91</v>
       </c>
       <c r="K21" t="n">
-        <v>10128185.26</v>
+        <v>4063875.06</v>
       </c>
       <c r="L21" t="n">
-        <v>1701359.46</v>
+        <v>947460.85</v>
       </c>
       <c r="M21" t="n">
-        <v>44.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="22">
@@ -1362,40 +1350,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12172599.71</v>
+        <v>4727314.96</v>
       </c>
       <c r="C22" t="n">
-        <v>5503221.39</v>
+        <v>4343299.8</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>78025.07000000001</v>
+        <v>54634.23</v>
       </c>
       <c r="F22" t="n">
-        <v>17753846.17</v>
+        <v>9125248.99</v>
       </c>
       <c r="G22" t="n">
-        <v>1281388.45</v>
+        <v>1382337.41</v>
       </c>
       <c r="H22" t="n">
-        <v>117037.6</v>
+        <v>81951.35000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>5457769.08</v>
+        <v>3209164.04</v>
       </c>
       <c r="J22" t="n">
-        <v>6856195.13</v>
+        <v>4673452.8</v>
       </c>
       <c r="K22" t="n">
-        <v>10897651.04</v>
+        <v>4451796.19</v>
       </c>
       <c r="L22" t="n">
-        <v>-1274948.67</v>
+        <v>-275518.77</v>
       </c>
       <c r="M22" t="n">
-        <v>-32.7</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="23">
@@ -1405,40 +1393,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11009718.31</v>
+        <v>4306038.8</v>
       </c>
       <c r="C23" t="n">
-        <v>6753026.19</v>
+        <v>5592230.8</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>90468.25999999999</v>
+        <v>69567.09</v>
       </c>
       <c r="F23" t="n">
-        <v>17853212.76</v>
+        <v>9967836.689999999</v>
       </c>
       <c r="G23" t="n">
-        <v>1968527.68</v>
+        <v>1523670.14</v>
       </c>
       <c r="H23" t="n">
-        <v>135702.38</v>
+        <v>104350.63</v>
       </c>
       <c r="I23" t="n">
-        <v>3962289.96</v>
+        <v>3396996.22</v>
       </c>
       <c r="J23" t="n">
-        <v>6066520.02</v>
+        <v>5025016.99</v>
       </c>
       <c r="K23" t="n">
-        <v>11786692.74</v>
+        <v>4942819.7</v>
       </c>
       <c r="L23" t="n">
-        <v>776974.4300000001</v>
+        <v>636780.9</v>
       </c>
       <c r="M23" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="24">
@@ -1448,40 +1436,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13133335.81</v>
+        <v>5259520.21</v>
       </c>
       <c r="C24" t="n">
-        <v>7359636.69</v>
+        <v>5043672.15</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>89411.17999999999</v>
+        <v>66157.64</v>
       </c>
       <c r="F24" t="n">
-        <v>20582383.68</v>
+        <v>10369350</v>
       </c>
       <c r="G24" t="n">
-        <v>1983679.12</v>
+        <v>1459236.41</v>
       </c>
       <c r="H24" t="n">
-        <v>134116.78</v>
+        <v>99236.46000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>5798879.91</v>
+        <v>3400493.46</v>
       </c>
       <c r="J24" t="n">
-        <v>7916675.81</v>
+        <v>4958966.33</v>
       </c>
       <c r="K24" t="n">
-        <v>12665707.87</v>
+        <v>5410383.67</v>
       </c>
       <c r="L24" t="n">
-        <v>-467627.94</v>
+        <v>150863.46</v>
       </c>
       <c r="M24" t="n">
-        <v>-10.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="25">
@@ -1491,40 +1479,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14458186.02</v>
+        <v>6353177.99</v>
       </c>
       <c r="C25" t="n">
-        <v>6483673.45</v>
+        <v>5329744.37</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>86966.82000000001</v>
+        <v>70062.03999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>21028826.29</v>
+        <v>11752984.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1919474.2</v>
+        <v>1462286.08</v>
       </c>
       <c r="H25" t="n">
-        <v>130450.23</v>
+        <v>105093.06</v>
       </c>
       <c r="I25" t="n">
-        <v>5457523.4</v>
+        <v>4280651.56</v>
       </c>
       <c r="J25" t="n">
-        <v>7507447.83</v>
+        <v>5848030.7</v>
       </c>
       <c r="K25" t="n">
-        <v>13521378.46</v>
+        <v>5904953.7</v>
       </c>
       <c r="L25" t="n">
-        <v>-936807.5600000001</v>
+        <v>-448224.29</v>
       </c>
       <c r="M25" t="n">
-        <v>-21.5</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="26">
@@ -1534,40 +1522,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14485053.4</v>
+        <v>6562163.76</v>
       </c>
       <c r="C26" t="n">
-        <v>4523824.26</v>
+        <v>3966956.53</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>65058.83</v>
+        <v>53828.75</v>
       </c>
       <c r="F26" t="n">
-        <v>19073936.49</v>
+        <v>10582949.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1295759.8</v>
+        <v>1164398.4</v>
       </c>
       <c r="H26" t="n">
-        <v>97588.25</v>
+        <v>80743.12</v>
       </c>
       <c r="I26" t="n">
-        <v>3513734.77</v>
+        <v>3050227.82</v>
       </c>
       <c r="J26" t="n">
-        <v>4907082.82</v>
+        <v>4295369.34</v>
       </c>
       <c r="K26" t="n">
-        <v>14166853.67</v>
+        <v>6287579.7</v>
       </c>
       <c r="L26" t="n">
-        <v>-318199.73</v>
+        <v>-274584.06</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="27">
@@ -1577,40 +1565,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14655087.47</v>
+        <v>6415586.22</v>
       </c>
       <c r="C27" t="n">
-        <v>5361016.35</v>
+        <v>4043032.39</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>69928.11</v>
+        <v>56764.06</v>
       </c>
       <c r="F27" t="n">
-        <v>20086031.93</v>
+        <v>10515382.67</v>
       </c>
       <c r="G27" t="n">
-        <v>1200792.32</v>
+        <v>1335819.1</v>
       </c>
       <c r="H27" t="n">
-        <v>104892.17</v>
+        <v>85146.09</v>
       </c>
       <c r="I27" t="n">
-        <v>3921152.11</v>
+        <v>2403892.46</v>
       </c>
       <c r="J27" t="n">
-        <v>5226836.6</v>
+        <v>3824857.65</v>
       </c>
       <c r="K27" t="n">
-        <v>14859195.33</v>
+        <v>6690525.02</v>
       </c>
       <c r="L27" t="n">
-        <v>204107.86</v>
+        <v>274938.8</v>
       </c>
       <c r="M27" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1620,40 +1608,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16680261.71</v>
+        <v>7483427.92</v>
       </c>
       <c r="C28" t="n">
-        <v>5390721.42</v>
+        <v>3863098.62</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>70754.67</v>
+        <v>55568.02</v>
       </c>
       <c r="F28" t="n">
-        <v>22141737.8</v>
+        <v>11402094.56</v>
       </c>
       <c r="G28" t="n">
-        <v>1555214.98</v>
+        <v>1192652.49</v>
       </c>
       <c r="H28" t="n">
-        <v>106132</v>
+        <v>83352.02</v>
       </c>
       <c r="I28" t="n">
-        <v>4920797.53</v>
+        <v>3040806.75</v>
       </c>
       <c r="J28" t="n">
-        <v>6582144.51</v>
+        <v>4316811.26</v>
       </c>
       <c r="K28" t="n">
-        <v>15559593.29</v>
+        <v>7085283.3</v>
       </c>
       <c r="L28" t="n">
-        <v>-1120668.42</v>
+        <v>-398144.62</v>
       </c>
       <c r="M28" t="n">
-        <v>-31.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="29">
@@ -1663,40 +1651,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16020957.08</v>
+        <v>7217302.73</v>
       </c>
       <c r="C29" t="n">
-        <v>5226646.73</v>
+        <v>4848848.72</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>77676.59</v>
+        <v>60751.72</v>
       </c>
       <c r="F29" t="n">
-        <v>21325280.4</v>
+        <v>12126903.17</v>
       </c>
       <c r="G29" t="n">
-        <v>1738666.27</v>
+        <v>1295380.5</v>
       </c>
       <c r="H29" t="n">
-        <v>116514.88</v>
+        <v>91127.59</v>
       </c>
       <c r="I29" t="n">
-        <v>3143536.24</v>
+        <v>3224520.28</v>
       </c>
       <c r="J29" t="n">
-        <v>4998717.39</v>
+        <v>4611028.37</v>
       </c>
       <c r="K29" t="n">
-        <v>16326563.01</v>
+        <v>7515874.8</v>
       </c>
       <c r="L29" t="n">
-        <v>305605.93</v>
+        <v>298572.07</v>
       </c>
       <c r="M29" t="n">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1706,40 +1694,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18210723.41</v>
+        <v>9112600.67</v>
       </c>
       <c r="C30" t="n">
-        <v>5642526.68</v>
+        <v>4466130.85</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>79854.45</v>
+        <v>60142.84</v>
       </c>
       <c r="F30" t="n">
-        <v>23933104.54</v>
+        <v>13638874.36</v>
       </c>
       <c r="G30" t="n">
-        <v>1490980.27</v>
+        <v>1235833.76</v>
       </c>
       <c r="H30" t="n">
-        <v>119781.68</v>
+        <v>90214.25</v>
       </c>
       <c r="I30" t="n">
-        <v>5207781.06</v>
+        <v>4370495.66</v>
       </c>
       <c r="J30" t="n">
-        <v>6818543.01</v>
+        <v>5696543.67</v>
       </c>
       <c r="K30" t="n">
-        <v>17114561.53</v>
+        <v>7942330.69</v>
       </c>
       <c r="L30" t="n">
-        <v>-1096161.88</v>
+        <v>-1170269.98</v>
       </c>
       <c r="M30" t="n">
-        <v>-27.5</v>
+        <v>-38.9</v>
       </c>
     </row>
     <row r="31">
@@ -1749,40 +1737,40 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18258052.33</v>
+        <v>9363202.970000001</v>
       </c>
       <c r="C31" t="n">
-        <v>5573500.08</v>
+        <v>4100750.77</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>74570.75</v>
+        <v>58028.89</v>
       </c>
       <c r="F31" t="n">
-        <v>23906123.16</v>
+        <v>13521982.63</v>
       </c>
       <c r="G31" t="n">
-        <v>1572494.4</v>
+        <v>1260458.47</v>
       </c>
       <c r="H31" t="n">
-        <v>111856.12</v>
+        <v>87043.33</v>
       </c>
       <c r="I31" t="n">
-        <v>4369814.75</v>
+        <v>3820214.87</v>
       </c>
       <c r="J31" t="n">
-        <v>6054165.27</v>
+        <v>5167716.67</v>
       </c>
       <c r="K31" t="n">
-        <v>17851957.89</v>
+        <v>8354265.96</v>
       </c>
       <c r="L31" t="n">
-        <v>-406094.44</v>
+        <v>-1008937.01</v>
       </c>
       <c r="M31" t="n">
-        <v>-10.9</v>
+        <v>-34.8</v>
       </c>
     </row>
     <row r="32">
@@ -1792,40 +1780,40 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18012243.75</v>
+        <v>8027917.37</v>
       </c>
       <c r="C32" t="n">
-        <v>6301941.04</v>
+        <v>5122756.28</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>79583.84</v>
+        <v>63355.32</v>
       </c>
       <c r="F32" t="n">
-        <v>24393768.63</v>
+        <v>13214028.97</v>
       </c>
       <c r="G32" t="n">
-        <v>1672541.27</v>
+        <v>1380586.26</v>
       </c>
       <c r="H32" t="n">
-        <v>119375.76</v>
+        <v>95032.98</v>
       </c>
       <c r="I32" t="n">
-        <v>3964250.39</v>
+        <v>2935390.42</v>
       </c>
       <c r="J32" t="n">
-        <v>5756167.42</v>
+        <v>4411009.66</v>
       </c>
       <c r="K32" t="n">
-        <v>18637601.21</v>
+        <v>8803019.310000001</v>
       </c>
       <c r="L32" t="n">
-        <v>625357.46</v>
+        <v>775101.9399999999</v>
       </c>
       <c r="M32" t="n">
-        <v>15.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="33">
@@ -1835,40 +1823,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18575361.95</v>
+        <v>8830758</v>
       </c>
       <c r="C33" t="n">
-        <v>6683100.81</v>
+        <v>4686759.5</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>81466.34</v>
+        <v>66065.3</v>
       </c>
       <c r="F33" t="n">
-        <v>25339929.1</v>
+        <v>13583582.8</v>
       </c>
       <c r="G33" t="n">
-        <v>1500361.93</v>
+        <v>1434759.65</v>
       </c>
       <c r="H33" t="n">
-        <v>122199.52</v>
+        <v>99097.95</v>
       </c>
       <c r="I33" t="n">
-        <v>4275929.72</v>
+        <v>2779188.01</v>
       </c>
       <c r="J33" t="n">
-        <v>5898491.17</v>
+        <v>4313045.61</v>
       </c>
       <c r="K33" t="n">
-        <v>19441437.93</v>
+        <v>9270537.189999999</v>
       </c>
       <c r="L33" t="n">
-        <v>866075.98</v>
+        <v>439779.19</v>
       </c>
       <c r="M33" t="n">
-        <v>21.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="34">
@@ -1878,40 +1866,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19248542.83</v>
+        <v>9855850.289999999</v>
       </c>
       <c r="C34" t="n">
-        <v>6206459.49</v>
+        <v>5227091.71</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>79567.53</v>
+        <v>66009.05</v>
       </c>
       <c r="F34" t="n">
-        <v>25534569.85</v>
+        <v>15148951.05</v>
       </c>
       <c r="G34" t="n">
-        <v>1731118.09</v>
+        <v>1441664.78</v>
       </c>
       <c r="H34" t="n">
-        <v>119351.29</v>
+        <v>99013.58</v>
       </c>
       <c r="I34" t="n">
-        <v>3456933.12</v>
+        <v>3870540.07</v>
       </c>
       <c r="J34" t="n">
-        <v>5307402.5</v>
+        <v>5411218.43</v>
       </c>
       <c r="K34" t="n">
-        <v>20227167.35</v>
+        <v>9737732.619999999</v>
       </c>
       <c r="L34" t="n">
-        <v>978624.52</v>
+        <v>-118117.67</v>
       </c>
       <c r="M34" t="n">
-        <v>24.6</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="35">
@@ -1921,40 +1909,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22974691.89</v>
+        <v>9577331.08</v>
       </c>
       <c r="C35" t="n">
-        <v>6481197.72</v>
+        <v>6340065.12</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>94666.41</v>
+        <v>76718.46000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>29550556.02</v>
+        <v>15994114.66</v>
       </c>
       <c r="G35" t="n">
-        <v>1650116.12</v>
+        <v>1865987.15</v>
       </c>
       <c r="H35" t="n">
-        <v>141999.62</v>
+        <v>115077.68</v>
       </c>
       <c r="I35" t="n">
-        <v>6600472.87</v>
+        <v>3734161.2</v>
       </c>
       <c r="J35" t="n">
-        <v>8392588.609999999</v>
+        <v>5715226.03</v>
       </c>
       <c r="K35" t="n">
-        <v>21157967.41</v>
+        <v>10278888.63</v>
       </c>
       <c r="L35" t="n">
-        <v>-1816724.48</v>
+        <v>701557.55</v>
       </c>
       <c r="M35" t="n">
-        <v>-38.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="36">
@@ -1964,40 +1952,40 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23661655.01</v>
+        <v>12428837.04</v>
       </c>
       <c r="C36" t="n">
-        <v>6451167.98</v>
+        <v>5368085.15</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>95949.35000000001</v>
+        <v>76616.02</v>
       </c>
       <c r="F36" t="n">
-        <v>30208772.34</v>
+        <v>17873538.21</v>
       </c>
       <c r="G36" t="n">
-        <v>2057569.2</v>
+        <v>1475564.56</v>
       </c>
       <c r="H36" t="n">
-        <v>143924.03</v>
+        <v>114924.03</v>
       </c>
       <c r="I36" t="n">
-        <v>5906074.11</v>
+        <v>5463646.13</v>
       </c>
       <c r="J36" t="n">
-        <v>8107567.34</v>
+        <v>7054134.72</v>
       </c>
       <c r="K36" t="n">
-        <v>22101205</v>
+        <v>10819403.49</v>
       </c>
       <c r="L36" t="n">
-        <v>-1560450.01</v>
+        <v>-1609433.55</v>
       </c>
       <c r="M36" t="n">
-        <v>-32.5</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="37">
@@ -2007,40 +1995,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23547032.47</v>
+        <v>12140794.24</v>
       </c>
       <c r="C37" t="n">
-        <v>6911431.68</v>
+        <v>6328290.97</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>94521.74000000001</v>
+        <v>80836.32000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>30552985.89</v>
+        <v>18549921.53</v>
       </c>
       <c r="G37" t="n">
-        <v>1845152.43</v>
+        <v>1686794.4</v>
       </c>
       <c r="H37" t="n">
-        <v>141782.61</v>
+        <v>121254.47</v>
       </c>
       <c r="I37" t="n">
-        <v>5535191.95</v>
+        <v>5352768.61</v>
       </c>
       <c r="J37" t="n">
-        <v>7522126.99</v>
+        <v>7160817.48</v>
       </c>
       <c r="K37" t="n">
-        <v>23030858.9</v>
+        <v>11389104.05</v>
       </c>
       <c r="L37" t="n">
-        <v>-516173.57</v>
+        <v>-751690.1899999999</v>
       </c>
       <c r="M37" t="n">
-        <v>-10.9</v>
+        <v>-18.6</v>
       </c>
     </row>
     <row r="38">
@@ -2050,40 +2038,40 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25303687.54</v>
+        <v>11523790.64</v>
       </c>
       <c r="C38" t="n">
-        <v>4588631</v>
+        <v>4763099.24</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>67938.22</v>
+        <v>61161.6</v>
       </c>
       <c r="F38" t="n">
-        <v>29960256.76</v>
+        <v>16348051.48</v>
       </c>
       <c r="G38" t="n">
-        <v>1194944.13</v>
+        <v>1469396.19</v>
       </c>
       <c r="H38" t="n">
-        <v>101907.33</v>
+        <v>91742.39</v>
       </c>
       <c r="I38" t="n">
-        <v>4957972.98</v>
+        <v>2963798.18</v>
       </c>
       <c r="J38" t="n">
-        <v>6254824.44</v>
+        <v>4524936.76</v>
       </c>
       <c r="K38" t="n">
-        <v>23705432.32</v>
+        <v>11823114.72</v>
       </c>
       <c r="L38" t="n">
-        <v>-1598255.22</v>
+        <v>299324.08</v>
       </c>
       <c r="M38" t="n">
-        <v>-47.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2093,40 +2081,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24114734.81</v>
+        <v>13161888.39</v>
       </c>
       <c r="C39" t="n">
-        <v>5148608.78</v>
+        <v>4355884.87</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>71467.17999999999</v>
+        <v>60902.62</v>
       </c>
       <c r="F39" t="n">
-        <v>29334810.77</v>
+        <v>17578675.88</v>
       </c>
       <c r="G39" t="n">
-        <v>1287930.68</v>
+        <v>1293907.48</v>
       </c>
       <c r="H39" t="n">
-        <v>107200.77</v>
+        <v>91353.92999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>3525674.26</v>
+        <v>3938010.37</v>
       </c>
       <c r="J39" t="n">
-        <v>4920805.71</v>
+        <v>5323271.78</v>
       </c>
       <c r="K39" t="n">
-        <v>24414005.06</v>
+        <v>12255404.1</v>
       </c>
       <c r="L39" t="n">
-        <v>299270.25</v>
+        <v>-906484.29</v>
       </c>
       <c r="M39" t="n">
-        <v>8.4</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="40">
@@ -2136,40 +2124,40 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26465779.64</v>
+        <v>12432609.7</v>
       </c>
       <c r="C40" t="n">
-        <v>4966334.47</v>
+        <v>4712988.48</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>69279.00999999999</v>
+        <v>59235.66</v>
       </c>
       <c r="F40" t="n">
-        <v>31501393.12</v>
+        <v>17204833.84</v>
       </c>
       <c r="G40" t="n">
-        <v>1521988.16</v>
+        <v>1257958.12</v>
       </c>
       <c r="H40" t="n">
-        <v>103918.52</v>
+        <v>88853.48</v>
       </c>
       <c r="I40" t="n">
-        <v>4773793.67</v>
+        <v>3181765.12</v>
       </c>
       <c r="J40" t="n">
-        <v>6399700.35</v>
+        <v>4528576.72</v>
       </c>
       <c r="K40" t="n">
-        <v>25101692.77</v>
+        <v>12676257.12</v>
       </c>
       <c r="L40" t="n">
-        <v>-1364086.87</v>
+        <v>243647.42</v>
       </c>
       <c r="M40" t="n">
-        <v>-39.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2179,40 +2167,40 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24977667.29</v>
+        <v>11979962.65</v>
       </c>
       <c r="C41" t="n">
-        <v>5592918.36</v>
+        <v>5285973.1</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>77412.09</v>
+        <v>65658.64999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>30647997.74</v>
+        <v>17331594.4</v>
       </c>
       <c r="G41" t="n">
-        <v>1291939.84</v>
+        <v>1260806.7</v>
       </c>
       <c r="H41" t="n">
-        <v>116118.13</v>
+        <v>98487.98</v>
       </c>
       <c r="I41" t="n">
-        <v>3372360.41</v>
+        <v>2830805.22</v>
       </c>
       <c r="J41" t="n">
-        <v>4780418.38</v>
+        <v>4190099.9</v>
       </c>
       <c r="K41" t="n">
-        <v>25867579.36</v>
+        <v>13141494.5</v>
       </c>
       <c r="L41" t="n">
-        <v>889912.0699999999</v>
+        <v>1161531.85</v>
       </c>
       <c r="M41" t="n">
-        <v>23</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="42">
@@ -2222,40 +2210,40 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27237846.83</v>
+        <v>14387519.42</v>
       </c>
       <c r="C42" t="n">
-        <v>5861500.95</v>
+        <v>5725491.48</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>72156.03999999999</v>
+        <v>69860.57000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>33171503.82</v>
+        <v>20182871.47</v>
       </c>
       <c r="G42" t="n">
-        <v>1251705.96</v>
+        <v>1622517.27</v>
       </c>
       <c r="H42" t="n">
-        <v>108234.07</v>
+        <v>104790.86</v>
       </c>
       <c r="I42" t="n">
-        <v>5228434.58</v>
+        <v>4819772.58</v>
       </c>
       <c r="J42" t="n">
-        <v>6588374.61</v>
+        <v>6547080.71</v>
       </c>
       <c r="K42" t="n">
-        <v>26583129.21</v>
+        <v>13635790.76</v>
       </c>
       <c r="L42" t="n">
-        <v>-654717.62</v>
+        <v>-751728.66</v>
       </c>
       <c r="M42" t="n">
-        <v>-18.1</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="43">
@@ -2265,40 +2253,40 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26726424.84</v>
+        <v>15439656.84</v>
       </c>
       <c r="C43" t="n">
-        <v>5594317.75</v>
+        <v>6070249.23</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>78952.59</v>
+        <v>73637.91</v>
       </c>
       <c r="F43" t="n">
-        <v>32399695.18</v>
+        <v>21583543.98</v>
       </c>
       <c r="G43" t="n">
-        <v>1579717.25</v>
+        <v>1896863.25</v>
       </c>
       <c r="H43" t="n">
-        <v>118428.89</v>
+        <v>110456.86</v>
       </c>
       <c r="I43" t="n">
-        <v>3337501.75</v>
+        <v>5420007.51</v>
       </c>
       <c r="J43" t="n">
-        <v>5035647.89</v>
+        <v>7427327.62</v>
       </c>
       <c r="K43" t="n">
-        <v>27364047.29</v>
+        <v>14156216.36</v>
       </c>
       <c r="L43" t="n">
-        <v>637622.45</v>
+        <v>-1283440.48</v>
       </c>
       <c r="M43" t="n">
-        <v>16.2</v>
+        <v>-34.9</v>
       </c>
     </row>
     <row r="44">
@@ -2308,40 +2296,40 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28652319.99</v>
+        <v>15719168.43</v>
       </c>
       <c r="C44" t="n">
-        <v>6112644.43</v>
+        <v>5795938.15</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>80911.61</v>
+        <v>75206.35000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>34845876.03</v>
+        <v>21590312.93</v>
       </c>
       <c r="G44" t="n">
-        <v>1443985.38</v>
+        <v>1613104.16</v>
       </c>
       <c r="H44" t="n">
-        <v>121367.41</v>
+        <v>112809.53</v>
       </c>
       <c r="I44" t="n">
-        <v>5116629.99</v>
+        <v>5176869.39</v>
       </c>
       <c r="J44" t="n">
-        <v>6681982.78</v>
+        <v>6902783.08</v>
       </c>
       <c r="K44" t="n">
-        <v>28163893.25</v>
+        <v>14687529.85</v>
       </c>
       <c r="L44" t="n">
-        <v>-488426.74</v>
+        <v>-1031638.58</v>
       </c>
       <c r="M44" t="n">
-        <v>-12.1</v>
+        <v>-27.4</v>
       </c>
     </row>
     <row r="45">
@@ -2351,40 +2339,40 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29936474.71</v>
+        <v>16573677.8</v>
       </c>
       <c r="C45" t="n">
-        <v>5768931.89</v>
+        <v>5510374.32</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>82971.19</v>
+        <v>75217.36</v>
       </c>
       <c r="F45" t="n">
-        <v>35788377.79</v>
+        <v>22159269.48</v>
       </c>
       <c r="G45" t="n">
-        <v>1834030.81</v>
+        <v>1795473.46</v>
       </c>
       <c r="H45" t="n">
-        <v>124456.79</v>
+        <v>112826.05</v>
       </c>
       <c r="I45" t="n">
-        <v>4846257.65</v>
+        <v>5031984.95</v>
       </c>
       <c r="J45" t="n">
-        <v>6804745.25</v>
+        <v>6940284.46</v>
       </c>
       <c r="K45" t="n">
-        <v>28983632.54</v>
+        <v>15218985.02</v>
       </c>
       <c r="L45" t="n">
-        <v>-952842.17</v>
+        <v>-1354692.78</v>
       </c>
       <c r="M45" t="n">
-        <v>-23</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="46">
@@ -2394,40 +2382,40 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29182922.99</v>
+        <v>16085771.85</v>
       </c>
       <c r="C46" t="n">
-        <v>6487814.29</v>
+        <v>5730568.51</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>86258.67999999999</v>
+        <v>76568.56</v>
       </c>
       <c r="F46" t="n">
-        <v>35756995.96</v>
+        <v>21892908.92</v>
       </c>
       <c r="G46" t="n">
-        <v>1865569.6</v>
+        <v>1734478.45</v>
       </c>
       <c r="H46" t="n">
-        <v>129388.01</v>
+        <v>114852.84</v>
       </c>
       <c r="I46" t="n">
-        <v>3926985.3</v>
+        <v>4283748.52</v>
       </c>
       <c r="J46" t="n">
-        <v>5921942.91</v>
+        <v>6133079.81</v>
       </c>
       <c r="K46" t="n">
-        <v>29835053.05</v>
+        <v>15759829.11</v>
       </c>
       <c r="L46" t="n">
-        <v>652130.0600000001</v>
+        <v>-325942.74</v>
       </c>
       <c r="M46" t="n">
-        <v>15.1</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="47">
@@ -2437,40 +2425,40 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31700311.04</v>
+        <v>15460125.74</v>
       </c>
       <c r="C47" t="n">
-        <v>8022319.74</v>
+        <v>6669409.83</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>96779.99000000001</v>
+        <v>85498.42</v>
       </c>
       <c r="F47" t="n">
-        <v>39819410.77</v>
+        <v>22215033.99</v>
       </c>
       <c r="G47" t="n">
-        <v>1672510.26</v>
+        <v>1686688.94</v>
       </c>
       <c r="H47" t="n">
-        <v>145169.99</v>
+        <v>128247.64</v>
       </c>
       <c r="I47" t="n">
-        <v>7214131.01</v>
+        <v>4037742.48</v>
       </c>
       <c r="J47" t="n">
-        <v>9031811.26</v>
+        <v>5852679.06</v>
       </c>
       <c r="K47" t="n">
-        <v>30787599.51</v>
+        <v>16362354.93</v>
       </c>
       <c r="L47" t="n">
-        <v>-912711.53</v>
+        <v>902229.1899999999</v>
       </c>
       <c r="M47" t="n">
-        <v>-18.9</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="48">
@@ -2480,40 +2468,40 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32971171.2</v>
+        <v>18306594.7</v>
       </c>
       <c r="C48" t="n">
-        <v>7037724.63</v>
+        <v>6074785.66</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>103528.47</v>
+        <v>90002.34</v>
       </c>
       <c r="F48" t="n">
-        <v>40112424.3</v>
+        <v>24471382.7</v>
       </c>
       <c r="G48" t="n">
-        <v>2290479.7</v>
+        <v>1715226.22</v>
       </c>
       <c r="H48" t="n">
-        <v>155292.7</v>
+        <v>135003.52</v>
       </c>
       <c r="I48" t="n">
-        <v>5861599.21</v>
+        <v>5625129.51</v>
       </c>
       <c r="J48" t="n">
-        <v>8307371.61</v>
+        <v>7475359.25</v>
       </c>
       <c r="K48" t="n">
-        <v>31805052.69</v>
+        <v>16996023.45</v>
       </c>
       <c r="L48" t="n">
-        <v>-1166118.51</v>
+        <v>-1310571.25</v>
       </c>
       <c r="M48" t="n">
-        <v>-22.5</v>
+        <v>-29.1</v>
       </c>
     </row>
     <row r="49">
@@ -2523,40 +2511,40 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31034709.67</v>
+        <v>18968114.18</v>
       </c>
       <c r="C49" t="n">
-        <v>9136272.58</v>
+        <v>7000183.33</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>110626.03</v>
+        <v>94970.28</v>
       </c>
       <c r="F49" t="n">
-        <v>40281608.28</v>
+        <v>26063267.79</v>
       </c>
       <c r="G49" t="n">
-        <v>1792108.45</v>
+        <v>2427345.02</v>
       </c>
       <c r="H49" t="n">
-        <v>165939.05</v>
+        <v>142455.42</v>
       </c>
       <c r="I49" t="n">
-        <v>5432796.96</v>
+        <v>5829430.93</v>
       </c>
       <c r="J49" t="n">
-        <v>7390844.46</v>
+        <v>8399231.369999999</v>
       </c>
       <c r="K49" t="n">
-        <v>32890763.82</v>
+        <v>17664036.42</v>
       </c>
       <c r="L49" t="n">
-        <v>1856054.15</v>
+        <v>-1304077.76</v>
       </c>
       <c r="M49" t="n">
-        <v>33.6</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="50">
@@ -2566,40 +2554,40 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31690875.81</v>
+        <v>19752392.7</v>
       </c>
       <c r="C50" t="n">
-        <v>6958989.16</v>
+        <v>5685162.95</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>85559.44</v>
+        <v>75927.63</v>
       </c>
       <c r="F50" t="n">
-        <v>38735424.41</v>
+        <v>25513483.28</v>
       </c>
       <c r="G50" t="n">
-        <v>1426213.73</v>
+        <v>1516371.32</v>
       </c>
       <c r="H50" t="n">
-        <v>128339.16</v>
+        <v>113891.44</v>
       </c>
       <c r="I50" t="n">
-        <v>3444914.5</v>
+        <v>5682499.8</v>
       </c>
       <c r="J50" t="n">
-        <v>4999467.39</v>
+        <v>7312762.56</v>
       </c>
       <c r="K50" t="n">
-        <v>33735957.02</v>
+        <v>18200720.72</v>
       </c>
       <c r="L50" t="n">
-        <v>2045081.21</v>
+        <v>-1551671.98</v>
       </c>
       <c r="M50" t="n">
-        <v>47.8</v>
+        <v>-40.9</v>
       </c>
     </row>
     <row r="51">
@@ -2609,40 +2597,40 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33517738.27</v>
+        <v>19141319.16</v>
       </c>
       <c r="C51" t="n">
-        <v>6855992.4</v>
+        <v>5977788.63</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>85802.27</v>
+        <v>77758.16</v>
       </c>
       <c r="F51" t="n">
-        <v>40459532.94</v>
+        <v>25196865.95</v>
       </c>
       <c r="G51" t="n">
-        <v>1663946.59</v>
+        <v>1498472.84</v>
       </c>
       <c r="H51" t="n">
-        <v>128703.41</v>
+        <v>116637.24</v>
       </c>
       <c r="I51" t="n">
-        <v>4083280.19</v>
+        <v>4831654.5</v>
       </c>
       <c r="J51" t="n">
-        <v>5875930.19</v>
+        <v>6446764.58</v>
       </c>
       <c r="K51" t="n">
-        <v>34583602.75</v>
+        <v>18750101.37</v>
       </c>
       <c r="L51" t="n">
-        <v>1065864.48</v>
+        <v>-391217.79</v>
       </c>
       <c r="M51" t="n">
-        <v>24.8</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="52">
@@ -2652,40 +2640,40 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>36714622.77</v>
+        <v>19416763.73</v>
       </c>
       <c r="C52" t="n">
-        <v>6573647.74</v>
+        <v>5060251.09</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>88853.28999999999</v>
+        <v>74507.69</v>
       </c>
       <c r="F52" t="n">
-        <v>43377123.8</v>
+        <v>24551522.51</v>
       </c>
       <c r="G52" t="n">
-        <v>2010767.74</v>
+        <v>1548911.55</v>
       </c>
       <c r="H52" t="n">
-        <v>133279.94</v>
+        <v>111761.53</v>
       </c>
       <c r="I52" t="n">
-        <v>5772416.52</v>
+        <v>3613729.98</v>
       </c>
       <c r="J52" t="n">
-        <v>7916464.2</v>
+        <v>5274403.06</v>
       </c>
       <c r="K52" t="n">
-        <v>35460659.6</v>
+        <v>19277119.45</v>
       </c>
       <c r="L52" t="n">
-        <v>-1253963.17</v>
+        <v>-139644.28</v>
       </c>
       <c r="M52" t="n">
-        <v>-28.2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="53">
@@ -2695,40 +2683,40 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>38466514.67</v>
+        <v>20237922.78</v>
       </c>
       <c r="C53" t="n">
-        <v>6123520.78</v>
+        <v>6194486.32</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>90473.61</v>
+        <v>82530.25</v>
       </c>
       <c r="F53" t="n">
-        <v>44680509.06</v>
+        <v>26514939.35</v>
       </c>
       <c r="G53" t="n">
-        <v>1858035.34</v>
+        <v>2063206.74</v>
       </c>
       <c r="H53" t="n">
-        <v>135710.41</v>
+        <v>123795.37</v>
       </c>
       <c r="I53" t="n">
-        <v>6333370.53</v>
+        <v>4468378.38</v>
       </c>
       <c r="J53" t="n">
-        <v>8327116.28</v>
+        <v>6655380.49</v>
       </c>
       <c r="K53" t="n">
-        <v>36353392.78</v>
+        <v>19859558.86</v>
       </c>
       <c r="L53" t="n">
-        <v>-2113121.89</v>
+        <v>-378363.92</v>
       </c>
       <c r="M53" t="n">
-        <v>-46.7</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2738,40 +2726,40 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>37914752.85</v>
+        <v>21117556.81</v>
       </c>
       <c r="C54" t="n">
-        <v>7962418.31</v>
+        <v>6329971.19</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>96879.02</v>
+        <v>87496.21000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>45974050.18</v>
+        <v>27535024.21</v>
       </c>
       <c r="G54" t="n">
-        <v>1786843.62</v>
+        <v>1690817.65</v>
       </c>
       <c r="H54" t="n">
-        <v>145318.53</v>
+        <v>131244.31</v>
       </c>
       <c r="I54" t="n">
-        <v>6734148.81</v>
+        <v>5236633.17</v>
       </c>
       <c r="J54" t="n">
-        <v>8666310.960000001</v>
+        <v>7058695.13</v>
       </c>
       <c r="K54" t="n">
-        <v>37307739.22</v>
+        <v>20476329.08</v>
       </c>
       <c r="L54" t="n">
-        <v>-607013.63</v>
+        <v>-641227.73</v>
       </c>
       <c r="M54" t="n">
-        <v>-12.5</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="55">
@@ -2781,40 +2769,40 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>39668756.59</v>
+        <v>22752044.63</v>
       </c>
       <c r="C55" t="n">
-        <v>6865554.27</v>
+        <v>5784330.87</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>97294.05</v>
+        <v>84017.28</v>
       </c>
       <c r="F55" t="n">
-        <v>46631604.91</v>
+        <v>28620392.78</v>
       </c>
       <c r="G55" t="n">
-        <v>2143177.33</v>
+        <v>1611467.43</v>
       </c>
       <c r="H55" t="n">
-        <v>145941.07</v>
+        <v>126025.92</v>
       </c>
       <c r="I55" t="n">
-        <v>6076295.18</v>
+        <v>5813739.1</v>
       </c>
       <c r="J55" t="n">
-        <v>8365413.58</v>
+        <v>7551232.45</v>
       </c>
       <c r="K55" t="n">
-        <v>38266191.33</v>
+        <v>21069160.33</v>
       </c>
       <c r="L55" t="n">
-        <v>-1402565.26</v>
+        <v>-1682884.3</v>
       </c>
       <c r="M55" t="n">
-        <v>-28.8</v>
+        <v>-40.1</v>
       </c>
     </row>
     <row r="56">
@@ -2824,40 +2812,40 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>40090372.82</v>
+        <v>22535428.95</v>
       </c>
       <c r="C56" t="n">
-        <v>6916172.37</v>
+        <v>6570844.94</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>100718.36</v>
+        <v>86633.35000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>47107263.55</v>
+        <v>29192907.24</v>
       </c>
       <c r="G56" t="n">
-        <v>1962068.27</v>
+        <v>1631871.13</v>
       </c>
       <c r="H56" t="n">
-        <v>151077.54</v>
+        <v>129950.02</v>
       </c>
       <c r="I56" t="n">
-        <v>5736479.61</v>
+        <v>5750977.96</v>
       </c>
       <c r="J56" t="n">
-        <v>7849625.42</v>
+        <v>7512799.11</v>
       </c>
       <c r="K56" t="n">
-        <v>39257638.13</v>
+        <v>21680108.13</v>
       </c>
       <c r="L56" t="n">
-        <v>-832734.6899999999</v>
+        <v>-855320.8199999999</v>
       </c>
       <c r="M56" t="n">
-        <v>-16.5</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="57">
@@ -2867,40 +2855,40 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>40342859.11</v>
+        <v>21710843.15</v>
       </c>
       <c r="C57" t="n">
-        <v>7304567.53</v>
+        <v>6557367.92</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>99706.56</v>
+        <v>88870.09</v>
       </c>
       <c r="F57" t="n">
-        <v>47747133.2</v>
+        <v>28357081.16</v>
       </c>
       <c r="G57" t="n">
-        <v>2146204.36</v>
+        <v>1916940.8</v>
       </c>
       <c r="H57" t="n">
-        <v>149559.84</v>
+        <v>133305.13</v>
       </c>
       <c r="I57" t="n">
-        <v>5211876.01</v>
+        <v>4000280.1</v>
       </c>
       <c r="J57" t="n">
-        <v>7507640.21</v>
+        <v>6050526.03</v>
       </c>
       <c r="K57" t="n">
-        <v>40239492.99</v>
+        <v>22306555.13</v>
       </c>
       <c r="L57" t="n">
-        <v>-103366.12</v>
+        <v>595711.98</v>
       </c>
       <c r="M57" t="n">
-        <v>-2.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="58">
@@ -2910,40 +2898,40 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43054353.06</v>
+        <v>24015759.93</v>
       </c>
       <c r="C58" t="n">
-        <v>6983265.67</v>
+        <v>6765911.2</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>101902.87</v>
+        <v>91069.63</v>
       </c>
       <c r="F58" t="n">
-        <v>50139521.6</v>
+        <v>30872740.76</v>
       </c>
       <c r="G58" t="n">
-        <v>1844605.8</v>
+        <v>2068303.23</v>
       </c>
       <c r="H58" t="n">
-        <v>152854.31</v>
+        <v>136604.45</v>
       </c>
       <c r="I58" t="n">
-        <v>6899507.66</v>
+        <v>5719588.46</v>
       </c>
       <c r="J58" t="n">
-        <v>8896967.77</v>
+        <v>7924496.14</v>
       </c>
       <c r="K58" t="n">
-        <v>41242553.83</v>
+        <v>22948244.62</v>
       </c>
       <c r="L58" t="n">
-        <v>-1811799.23</v>
+        <v>-1067515.31</v>
       </c>
       <c r="M58" t="n">
-        <v>-35.6</v>
+        <v>-23.4</v>
       </c>
     </row>
     <row r="59">
@@ -2953,40 +2941,40 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>41807639.08</v>
+        <v>24749614.74</v>
       </c>
       <c r="C59" t="n">
-        <v>9378052.59</v>
+        <v>9379994.539999999</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>115605.58</v>
+        <v>113138.94</v>
       </c>
       <c r="F59" t="n">
-        <v>51301297.25</v>
+        <v>34242748.22</v>
       </c>
       <c r="G59" t="n">
-        <v>2356520.03</v>
+        <v>2544921.19</v>
       </c>
       <c r="H59" t="n">
-        <v>173408.37</v>
+        <v>169708.41</v>
       </c>
       <c r="I59" t="n">
-        <v>6394086.87</v>
+        <v>7785840.61</v>
       </c>
       <c r="J59" t="n">
-        <v>8924015.27</v>
+        <v>10500470.21</v>
       </c>
       <c r="K59" t="n">
-        <v>42377281.98</v>
+        <v>23742278.01</v>
       </c>
       <c r="L59" t="n">
-        <v>569642.9</v>
+        <v>-1007336.73</v>
       </c>
       <c r="M59" t="n">
-        <v>9.9</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="60">
@@ -2996,40 +2984,40 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>42314705.55</v>
+        <v>24757739.84</v>
       </c>
       <c r="C60" t="n">
-        <v>9150565.6</v>
+        <v>7118984.62</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>123508.84</v>
+        <v>106475.16</v>
       </c>
       <c r="F60" t="n">
-        <v>51588779.99</v>
+        <v>31983199.62</v>
       </c>
       <c r="G60" t="n">
-        <v>2532879.57</v>
+        <v>2115014.39</v>
       </c>
       <c r="H60" t="n">
-        <v>185263.26</v>
+        <v>159712.74</v>
       </c>
       <c r="I60" t="n">
-        <v>5282634.43</v>
+        <v>5218075.49</v>
       </c>
       <c r="J60" t="n">
-        <v>8000777.26</v>
+        <v>7492802.62</v>
       </c>
       <c r="K60" t="n">
-        <v>43588002.73</v>
+        <v>24490397</v>
       </c>
       <c r="L60" t="n">
-        <v>1273297.18</v>
+        <v>-267342.84</v>
       </c>
       <c r="M60" t="n">
-        <v>20.6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="61">
@@ -3039,40 +3027,40 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>44801221.68</v>
+        <v>24988416.19</v>
       </c>
       <c r="C61" t="n">
-        <v>9757656.48</v>
+        <v>8829223.939999999</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>126035.34</v>
+        <v>112180.71</v>
       </c>
       <c r="F61" t="n">
-        <v>54684913.5</v>
+        <v>33929820.84</v>
       </c>
       <c r="G61" t="n">
-        <v>2734211.06</v>
+        <v>2223664.41</v>
       </c>
       <c r="H61" t="n">
-        <v>189053.02</v>
+        <v>168271.06</v>
       </c>
       <c r="I61" t="n">
-        <v>6938550.12</v>
+        <v>6259935.44</v>
       </c>
       <c r="J61" t="n">
-        <v>9861814.199999999</v>
+        <v>8651870.91</v>
       </c>
       <c r="K61" t="n">
-        <v>44823099.3</v>
+        <v>25277949.93</v>
       </c>
       <c r="L61" t="n">
-        <v>21877.62</v>
+        <v>289533.74</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="62">
@@ -3082,40 +3070,83 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>45962230.7</v>
+        <v>27633593.98</v>
       </c>
       <c r="C62" t="n">
-        <v>7319927.28</v>
+        <v>6022580.94</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>93866.64</v>
+        <v>85222.28</v>
       </c>
       <c r="F62" t="n">
-        <v>53376024.62</v>
+        <v>33741397.2</v>
       </c>
       <c r="G62" t="n">
-        <v>2044253.93</v>
+        <v>1728475.88</v>
       </c>
       <c r="H62" t="n">
-        <v>140799.96</v>
+        <v>127833.41</v>
       </c>
       <c r="I62" t="n">
-        <v>5441473.07</v>
+        <v>6005532.55</v>
       </c>
       <c r="J62" t="n">
-        <v>7626526.96</v>
+        <v>7861841.84</v>
       </c>
       <c r="K62" t="n">
-        <v>45749497.66</v>
+        <v>25879555.36</v>
       </c>
       <c r="L62" t="n">
-        <v>-212733.04</v>
+        <v>-1754038.62</v>
       </c>
       <c r="M62" t="n">
-        <v>-4.5</v>
+        <v>-41.2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>27576137.3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5693644.51</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>85291.71000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>33355073.52</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1986978.94</v>
+      </c>
+      <c r="H63" t="n">
+        <v>127937.56</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4758451.49</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6873367.99</v>
+      </c>
+      <c r="K63" t="n">
+        <v>26481705.53</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-1094431.77</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-25.7</v>
       </c>
     </row>
   </sheetData>
